--- a/outputs/evaluation/CF_M08_req_eval_gt_report.xlsx
+++ b/outputs/evaluation/CF_M08_req_eval_gt_report.xlsx
@@ -503,11 +503,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Company products, routes, and profiles can only be edited and accessed by that company.</t>
+          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2641</v>
+        <v>0.2492</v>
       </c>
     </row>
     <row r="3">
@@ -536,16 +536,16 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R_05</t>
+          <t>R_06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The system shall allow users to log out.</t>
+          <t>The system shall allow logged-in users to view company profiles and their products.</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3063</v>
+        <v>0.2993</v>
       </c>
     </row>
     <row r="4">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.6026</v>
+        <v>0.6064000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2115</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="6">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.3108</v>
+        <v>0.3132</v>
       </c>
     </row>
     <row r="7">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.195</v>
+        <v>0.1928</v>
       </c>
     </row>
     <row r="8">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.2884</v>
+        <v>0.3026</v>
       </c>
     </row>
     <row r="9">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.4844</v>
+        <v>0.4777</v>
       </c>
     </row>
     <row r="10">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.8568</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="11">
@@ -854,11 +854,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Uptime monitoring demonstrating 99.9% availability and disaster recovery tests meeting the specified recovery time.</t>
+          <t>Uptime monitoring demonstrating 99.9% uptime and disaster recovery tests meeting the specified recovery time.</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.5174</v>
+        <v>0.6267</v>
       </c>
     </row>
     <row r="12">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.639</v>
+        <v>0.6394</v>
       </c>
     </row>
     <row r="13">
@@ -932,11 +932,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Complete and updated documentation, with an average time for implementing updates and resolving issues not exceeding 2 hours.</t>
+          <t>Complete and updated documentation, and average time for implementation of updates and troubleshooting not exceeding 2 hours.</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.5151</v>
+        <v>0.5613</v>
       </c>
     </row>
     <row r="14">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.5809</v>
+        <v>0.579</v>
       </c>
     </row>
     <row r="15">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.5409</v>
+        <v>0.5412</v>
       </c>
     </row>
     <row r="16">
@@ -1067,11 +1067,11 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Company products, routes, and profiles can only be edited and accessed by that company.</t>
+          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6555</v>
       </c>
     </row>
     <row r="17">
@@ -1114,11 +1114,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Company products, routes, and profiles can only be edited and accessed by that company.</t>
+          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.6633</v>
+        <v>0.6281</v>
       </c>
     </row>
     <row r="18">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.3744</v>
+        <v>0.3754</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M08_req_eval_gt_report.xlsx
+++ b/outputs/evaluation/CF_M08_req_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2492</v>
+        <v>0.2518</v>
       </c>
     </row>
     <row r="3">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.2993</v>
+        <v>0.3008</v>
       </c>
     </row>
     <row r="4">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.6103</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2143</v>
+        <v>0.2157</v>
       </c>
     </row>
     <row r="6">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.3132</v>
+        <v>0.3147</v>
       </c>
     </row>
     <row r="7">
@@ -687,16 +687,16 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_17a</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
+          <t>The system must have 99.9% uptime.</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.1928</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="8">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.3026</v>
+        <v>0.3029</v>
       </c>
     </row>
     <row r="9">
@@ -789,50 +789,59 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_R21a</t>
+          <t>CF_M08_R24b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The system must be able to recover from failures
-in less than 1 hour.</t>
+          <t>The system must be compatible with the
+most common mobile devices.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>14c. Adaptability requirements</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>R_17</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>The system must have 99.9% uptime and be able to recover from failures in less than 1 hour.</t>
+          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.856</v>
+        <v>0.5810999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_R21b</t>
+          <t>CF_M08_R25a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Uptime monitoring that demonstrates 99.9% uptime.</t>
+          <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox,
+Safari, Edge).</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -841,321 +850,159 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CF_M08_R24a</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>R_18</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Uptime monitoring demonstrating 99.9% uptime and disaster recovery tests meeting the specified recovery time.</t>
+          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.6267</v>
+        <v>0.5402</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M08_R22a</t>
+          <t>CF_M08_R28a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The system must be easy to maintain and update.</t>
+          <t>The products of a company
+they can only be edited and accessible by that
+company.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>15a. Access Requirement</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>R_19</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>The system must be easy to maintain and update with clear and complete documentation.</t>
+          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.6394</v>
+        <v>0.6581</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M08_R23</t>
+          <t>CF_M08_R28b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Average implementation time of updates and error fixes no more than 2 hours.</t>
+          <t>The routes of a company
+they can only be edited and accessible by that
+company.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CF_M08_R22a</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>15a. Access Requirement</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>R_20</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Complete and updated documentation, and average time for implementation of updates and troubleshooting not exceeding 2 hours.</t>
+          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.5613</v>
+        <v>0.6304</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M08_R24b</t>
+          <t>CF_M08_R29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The system must be compatible with the
-most common mobile devices.</t>
+          <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Constraint</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>14c. Adaptability requirements</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>R_21</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
+          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.579</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CF_M08_R25a</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox,
-Safari, Edge).</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>33</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CF_M08_R24a</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>R_21</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0.5412</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CF_M08_R28a</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The products of a company
-they can only be edited and accessible by that
-company.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>33</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>15a. Access Requirement</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>0.6555</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CF_M08_R28b</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The routes of a company
-they can only be edited and accessible by that
-company.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>33</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>15a. Access Requirement</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0.6281</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CF_M08_R29</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>The system should have three different membership plans: free, basic and premium.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>31</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>R_12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0.3754</v>
+        <v>0.3756</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M08_req_eval_gt_report.xlsx
+++ b/outputs/evaluation/CF_M08_req_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.2518</v>
+        <v>0.2433</v>
       </c>
     </row>
     <row r="3">
@@ -518,8 +518,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The system must be able to save all the images of all the products and users of the
-system.</t>
+          <t>The system must be able to save all the images of all the products and users of the system.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,18 +544,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.3008</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_R07a</t>
+          <t>CF_M08_R12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A company must be able to modify its public profile/page at any time.</t>
+          <t>Every product must have a predetermined route in which the user returns it on his own account and with his own means.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -565,7 +564,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -573,28 +572,27 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A company shall be able to modify its public profile at any time and preview it while editing.</t>
+          <t>A user shall be able to return a product registered by a company using its routes.</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.6103</v>
+        <v>0.2208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_R12</t>
+          <t>CF_M08_R13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Every product must have a predetermined route in which the user returns it
-on his own account and with his own means.</t>
+          <t>Every route must have an associated budget (can be 0) which the user must be able to pay using the system when returning the product.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -620,19 +618,18 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2157</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_R13</t>
+          <t>CF_M08_R14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Every route must have an associated budget (can be 0) which the user must
-be able to pay using the system when returning the product.</t>
+          <t>The system must have a membership system/plans for companies that want to have certain advantages.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -649,175 +646,181 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>R_11</t>
+          <t>R_17a</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>A user shall be able to return a product registered by a company using its routes.</t>
+          <t>The system must have 99.9% uptime.</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.3147</v>
+        <v>0.2052</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_R14</t>
+          <t>CF_M08_R15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The system must have a membership system/plans for companies that want to
-have certain advantages.</t>
+          <t>The system must be available in different languages</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>31</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11b. Personalization and Internal Requirements
+nationalization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>R_17a</t>
+          <t>R_01a</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The system must have 99.9% uptime.</t>
+          <t>The system shall be available in Spanish.</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.2121</v>
+        <v>0.3546</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_R15</t>
+          <t>CF_M08_R22b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The system must be available in different languages</t>
+          <t>Complete and updated documentation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>11b. Personalization and Internal Requirements
-nationalization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_19b</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>The system shall be available in both Spanish and English.</t>
+          <t>The system must have clear and complete documentation.</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.3029</v>
+        <v>0.6655</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_R16a</t>
+          <t>CF_M08_R24b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The system should support Spanish (verified by a translator).</t>
+          <t>The system must be compatible with the most common mobile devices.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>CF_M08_R15</t>
-        </is>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>14c. Adaptability requirements</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>R_02</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>The system interface shall be available in Spanish and English, verified by a translator.</t>
+          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.4777</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_R24b</t>
+          <t>CF_M08_R25a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The system must be compatible with the
-most common mobile devices.</t>
+          <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge).</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>33</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>14c. Adaptability requirements</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CF_M08_R24a</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_21</t>
@@ -829,62 +832,67 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_R25a</t>
+          <t>CF_M08_R28a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox,
-Safari, Edge).</t>
+          <t>The products of a company can only be edited and accessible by that company.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>33</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>CF_M08_R24a</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15a. Access Requirement</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>R_21</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>The system must be compatible with common web browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
+          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.5402</v>
+        <v>0.6725</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M08_R28a</t>
+          <t>CF_M08_R28b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The products of a company
-they can only be edited and accessible by that
-company.</t>
+          <t>The routes of a company can only be edited and accessible by that company.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -906,7 +914,11 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>R_25</t>
@@ -918,91 +930,48 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.6581</v>
+        <v>0.6446</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M08_R28b</t>
+          <t>CF_M08_R29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The routes of a company
-they can only be edited and accessible by that
-company.</t>
+          <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Constraint</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>15a. Access Requirement</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Classification changed</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>R_25</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Company products/routes/profile can only be edited and accessed by that company.</t>
+          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.6304</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M08_R29</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The system should have three different membership plans: free, basic and premium.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>31</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>R_12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>The system shall provide an affiliation/plan system for companies (free, basic, and premium).</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0.3756</v>
+        <v>0.3764</v>
       </c>
     </row>
   </sheetData>
